--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="15564" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="宋体"/>
@@ -622,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -630,6 +632,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1008,9 +1014,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11.625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,96 +1033,80 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45391</v>
+        <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>45752</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>1.0045</v>
+        <v>0.7111499999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.73668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.9959</v>
+        <v>0.71105</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1.0045</v>
+        <v>0.8003</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
@@ -1124,9 +1114,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
@@ -1134,9 +1124,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B13" s="0" t="n">
@@ -1144,9 +1134,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B14" s="0" t="n">
@@ -1154,34 +1144,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="n">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>0.9959</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>0.9959</v>
-      </c>
+      <c r="A16" s="0" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.9959</v>
-      </c>
+      <c r="A17" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1195,8 +1171,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1212,96 +1188,80 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45391</v>
+        <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>1</v>
+        <v>0.3002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1.132</v>
+        <v>0.4115</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1.132</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>1.132</v>
+        <v>0.45555</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>45752</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>1.132</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>1.132</v>
+        <v>0.60005</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1.132</v>
+        <v>0.73115</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>1.132</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1.132</v>
+        <v>0.8006</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
@@ -1309,9 +1269,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
@@ -1319,9 +1279,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B13" s="0" t="n">
@@ -1329,9 +1289,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B14" s="0" t="n">
@@ -1339,42 +1299,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="n">
-        <v>1.132</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>1.132</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>1.132</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1.132</v>
       </c>
     </row>
@@ -1391,9 +1321,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="13.125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.1296296296296" customWidth="1" style="1" min="1" max="1"/>
     <col width="15" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1411,96 +1341,80 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45391</v>
+        <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>1</v>
+        <v>0.1555</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.23331</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.45555</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>45752</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.5023</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.6112</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.7211</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1.0029</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
@@ -1508,9 +1422,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
@@ -1518,9 +1432,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B13" s="0" t="n">
@@ -1528,9 +1442,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B14" s="0" t="n">
@@ -1538,9 +1452,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B15" s="0" t="n">
@@ -1548,24 +1462,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>1.0029</v>
-      </c>
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.0029</v>
-      </c>
+      <c r="A17" s="0" t="n"/>
+      <c r="B17" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1580,7 +1482,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
   </cols>
@@ -1599,96 +1501,80 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45391</v>
+        <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>1</v>
+        <v>0.08550000000000001</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>2</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>2</v>
+        <v>0.3222</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>2</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>45752</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>2</v>
+        <v>0.5538</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>2</v>
+        <v>0.6223</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>2</v>
+        <v>0.7488</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>2</v>
+        <v>0.9211</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>2</v>
+        <v>0.8245</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
@@ -1696,9 +1582,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
@@ -1706,9 +1592,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B13" s="0" t="n">
@@ -1716,9 +1602,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B14" s="0" t="n">
@@ -1726,44 +1612,23 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="n">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>2</v>
-      </c>
+      <c r="A16" s="0" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>2</v>
-      </c>
+      <c r="A17" s="0" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
+      <c r="A18" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="15564" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1013,10 +1013,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1036,7 +1036,7 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="3">
@@ -1149,15 +1149,439 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>0.9959</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>0.9959</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.9959</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1171,8 +1595,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1191,7 +1615,7 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.3002</v>
+        <v>0.98002</v>
       </c>
     </row>
     <row r="3">
@@ -1304,7 +1728,437 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
         <v>1.132</v>
       </c>
     </row>
@@ -1320,10 +2174,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.1296296296296" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.1333333333333" customWidth="1" style="1" min="1" max="1"/>
     <col width="15" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1344,7 +2198,7 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.1555</v>
+        <v>0.9555</v>
       </c>
     </row>
     <row r="3">
@@ -1462,12 +2316,434 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="n"/>
-      <c r="B16" s="0" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>1.0029</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="n"/>
-      <c r="B17" s="0" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>1.0029</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.0029</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1481,8 +2757,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B58"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
   </cols>
@@ -1504,7 +2780,7 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.9855</v>
       </c>
     </row>
     <row r="3">
@@ -1617,18 +2893,439 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -1312,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.1333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -1338,9 +1338,6 @@
       <c r="B2" s="0" t="n">
         <v>0.51555</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1349,9 +1346,6 @@
       <c r="B3" s="0" t="n">
         <v>0.23331</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.5474541751527494</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1360,9 +1354,6 @@
       <c r="B4" s="0" t="n">
         <v>0.3815</v>
       </c>
-      <c r="C4" t="n">
-        <v>-0.2600135777325186</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1371,9 +1362,6 @@
       <c r="B5" s="0" t="n">
         <v>0.45555</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.1163805644457375</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1382,9 +1370,6 @@
       <c r="B6" s="0" t="n">
         <v>0.5023</v>
       </c>
-      <c r="C6" t="n">
-        <v>-0.02570070798176701</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1393,9 +1378,6 @@
       <c r="B7" s="0" t="n">
         <v>0.6112</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1404,9 +1386,6 @@
       <c r="B8" s="0" t="n">
         <v>0.7211</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1415,9 +1394,6 @@
       <c r="B9" s="0" t="n">
         <v>0.9883</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1426,22 +1402,10 @@
       <c r="B10" s="0" t="n">
         <v>0.8445</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.1455023778204998</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>1.0029</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n"/>
@@ -1479,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1504,9 +1468,6 @@
       <c r="B2" s="0" t="n">
         <v>0.4855</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1515,9 +1476,6 @@
       <c r="B3" s="0" t="n">
         <v>0.2112</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.5649845520082389</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1526,9 +1484,6 @@
       <c r="B4" s="0" t="n">
         <v>0.3222</v>
       </c>
-      <c r="C4" t="n">
-        <v>-0.3363542739443872</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1537,9 +1492,6 @@
       <c r="B5" s="0" t="n">
         <v>0.4112</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.1530381050463439</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1548,9 +1500,6 @@
       <c r="B6" s="0" t="n">
         <v>0.5538</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1559,9 +1508,6 @@
       <c r="B7" s="0" t="n">
         <v>0.6223</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1570,9 +1516,6 @@
       <c r="B8" s="0" t="n">
         <v>0.7488</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1581,9 +1524,6 @@
       <c r="B9" s="0" t="n">
         <v>0.9211</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1592,22 +1532,9 @@
       <c r="B10" s="0" t="n">
         <v>0.8245</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.1048746064488112</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n"/>

--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-收盘数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化二-结算数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量化二-收盘数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -624,7 +625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -636,6 +637,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1013,11 +1022,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1036,9 +1042,9 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C2" t="n">
+        <v>0.63002</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1047,9 +1053,9 @@
         <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C3" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <v>-0.2666666666666666</v>
       </c>
     </row>
@@ -1058,9 +1064,9 @@
         <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="C4" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>-0.2266666666666667</v>
       </c>
     </row>
@@ -1069,9 +1075,9 @@
         <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="C5" t="n">
+        <v>0.45555</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <v>-0.1733333333333333</v>
       </c>
     </row>
@@ -1082,7 +1088,7 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>-0.1066666666666666</v>
       </c>
     </row>
@@ -1091,9 +1097,9 @@
         <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.7111499999999999</v>
-      </c>
-      <c r="C7" t="n">
+        <v>0.60005</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <v>-0.05180000000000007</v>
       </c>
     </row>
@@ -1102,9 +1108,9 @@
         <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.73668</v>
-      </c>
-      <c r="C8" t="n">
+        <v>0.73115</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <v>-0.01776</v>
       </c>
     </row>
@@ -1113,9 +1119,9 @@
         <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.71105</v>
-      </c>
-      <c r="C9" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <v>-0.05193333333333339</v>
       </c>
     </row>
@@ -1124,42 +1130,76 @@
         <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8003</v>
-      </c>
-      <c r="C10" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="C10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.9959</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="0" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="C11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="n"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1173,8 +1213,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1193,9 +1236,9 @@
         <v>45748</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.63002</v>
-      </c>
-      <c r="C2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1204,9 +1247,9 @@
         <v>45749</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.4115</v>
-      </c>
-      <c r="C3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <v>-0.3468461318688296</v>
       </c>
     </row>
@@ -1215,9 +1258,9 @@
         <v>45750</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.4333</v>
-      </c>
-      <c r="C4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>-0.3122440557442621</v>
       </c>
     </row>
@@ -1226,9 +1269,9 @@
         <v>45751</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.45555</v>
-      </c>
-      <c r="C5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <v>-0.276927716580426</v>
       </c>
     </row>
@@ -1239,7 +1282,7 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1248,9 +1291,9 @@
         <v>45753</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.60005</v>
-      </c>
-      <c r="C7" t="n">
+        <v>0.7111499999999999</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <v>-0.104402985074627</v>
       </c>
     </row>
@@ -1259,9 +1302,9 @@
         <v>45754</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.73115</v>
-      </c>
-      <c r="C8" t="n">
+        <v>0.73668</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1270,9 +1313,9 @@
         <v>45755</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.9115</v>
-      </c>
-      <c r="C9" t="n">
+        <v>0.71105</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1281,24 +1324,82 @@
         <v>45756</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8006</v>
-      </c>
-      <c r="C10" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="C10" s="0" t="n">
         <v>-0.121667580910587</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="0" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C11" s="0" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1307,6 +1408,131 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>0.4855</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45749</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.2112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45750</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.3222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45751</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.4112</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0.5538</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45753</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.6223</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.7488</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.9211</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45756</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.8245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1435,129 +1661,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="16.6666666666667" customWidth="1" style="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>0.4855</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45749</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>0.2112</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45750</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>0.3222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45751</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>0.4112</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45752</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>0.5538</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45753</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>0.6223</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45754</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>0.7488</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>0.9211</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45756</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>0.8245</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -625,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -637,14 +636,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1047,7 +1038,7 @@
       <c r="B2" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1060,9 +1051,9 @@
       <c r="B3" s="0" t="n">
         <v>0.55</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>-34.6846%</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-26.6667%</t>
         </is>
       </c>
     </row>
@@ -1073,9 +1064,9 @@
       <c r="B4" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>-31.2244%</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-22.6667%</t>
         </is>
       </c>
     </row>
@@ -1086,9 +1077,9 @@
       <c r="B5" s="0" t="n">
         <v>0.62</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>-27.6928%</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-17.3333%</t>
         </is>
       </c>
     </row>
@@ -1099,9 +1090,9 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-10.6667%</t>
         </is>
       </c>
     </row>
@@ -1112,9 +1103,9 @@
       <c r="B7" s="0" t="n">
         <v>0.7111499999999999</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>-10.4403%</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-5.18%</t>
         </is>
       </c>
     </row>
@@ -1125,9 +1116,9 @@
       <c r="B8" s="0" t="n">
         <v>0.73668</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1.776%</t>
         </is>
       </c>
     </row>
@@ -1138,9 +1129,9 @@
       <c r="B9" s="0" t="n">
         <v>0.71105</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-5.1933%</t>
         </is>
       </c>
     </row>
@@ -1151,41 +1142,29 @@
       <c r="B10" s="0" t="n">
         <v>0.8003</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>-12.1668%</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" t="n">
         <v>1.13204</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.13204</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="A12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n"/>
@@ -1214,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1215,7 @@
       <c r="B2" s="0" t="n">
         <v>0.63002</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1249,9 +1228,9 @@
       <c r="B3" s="0" t="n">
         <v>0.4115</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>-26.6667%</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-34.6846%</t>
         </is>
       </c>
     </row>
@@ -1262,9 +1241,9 @@
       <c r="B4" s="0" t="n">
         <v>0.4333</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>-22.6667%</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-31.2244%</t>
         </is>
       </c>
     </row>
@@ -1275,9 +1254,9 @@
       <c r="B5" s="0" t="n">
         <v>0.45555</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>-17.3333%</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-27.6928%</t>
         </is>
       </c>
     </row>
@@ -1288,9 +1267,9 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>-10.6667%</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1301,9 +1280,9 @@
       <c r="B7" s="0" t="n">
         <v>0.60005</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>-5.18%</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-10.4403%</t>
         </is>
       </c>
     </row>
@@ -1314,9 +1293,9 @@
       <c r="B8" s="0" t="n">
         <v>0.73115</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>-1.776%</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1327,9 +1306,9 @@
       <c r="B9" s="0" t="n">
         <v>0.9115</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>-5.1933%</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1340,39 +1319,24 @@
       <c r="B10" s="0" t="n">
         <v>0.8006</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-12.1668%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.99593</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-12.0234%</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1378,7 @@
       <c r="B2" s="0" t="n">
         <v>0.51555</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1427,9 +1391,9 @@
       <c r="B3" s="0" t="n">
         <v>0.23331</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>-56.4985%</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-54.7454%</t>
         </is>
       </c>
     </row>
@@ -1440,9 +1404,9 @@
       <c r="B4" s="0" t="n">
         <v>0.3815</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>-33.6354%</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-26.0014%</t>
         </is>
       </c>
     </row>
@@ -1453,9 +1417,9 @@
       <c r="B5" s="0" t="n">
         <v>0.45555</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>-15.3038%</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-11.6381%</t>
         </is>
       </c>
     </row>
@@ -1466,9 +1430,9 @@
       <c r="B6" s="0" t="n">
         <v>0.5023</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-2.5701%</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1443,7 @@
       <c r="B7" s="0" t="n">
         <v>0.6112</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1492,7 +1456,7 @@
       <c r="B8" s="0" t="n">
         <v>0.7211</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1505,7 +1469,7 @@
       <c r="B9" s="0" t="n">
         <v>0.9883</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1518,14 +1482,14 @@
       <c r="B10" s="0" t="n">
         <v>0.8445</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>-10.4875%</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-14.5502%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -1533,26 +1497,15 @@
       <c r="B11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n"/>
@@ -1611,7 +1564,7 @@
       <c r="B2" s="0" t="n">
         <v>0.4855</v>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1624,9 +1577,9 @@
       <c r="B3" s="0" t="n">
         <v>0.2112</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>-54.7454%</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-56.4985%</t>
         </is>
       </c>
     </row>
@@ -1637,9 +1590,9 @@
       <c r="B4" s="0" t="n">
         <v>0.3222</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>-26.0014%</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-33.6354%</t>
         </is>
       </c>
     </row>
@@ -1650,9 +1603,9 @@
       <c r="B5" s="0" t="n">
         <v>0.4112</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>-11.6381%</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-15.3038%</t>
         </is>
       </c>
     </row>
@@ -1663,9 +1616,9 @@
       <c r="B6" s="0" t="n">
         <v>0.5538</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>-2.5701%</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1629,7 @@
       <c r="B7" s="0" t="n">
         <v>0.6223</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1689,7 +1642,7 @@
       <c r="B8" s="0" t="n">
         <v>0.7488</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1702,7 +1655,7 @@
       <c r="B9" s="0" t="n">
         <v>0.9211</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1715,41 +1668,29 @@
       <c r="B10" s="0" t="n">
         <v>0.8245</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>-14.5502%</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-10.4875%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" t="n">
         <v>1.00286</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2025/04/10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.00286</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-49.857%</t>
-        </is>
-      </c>
+      <c r="A12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n"/>

--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -1184,17 +1184,29 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>1.13204</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n"/>
@@ -1217,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1385,10 +1397,25 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1581,15 +1608,26 @@
       <c r="B13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n"/>
-      <c r="B14" s="0" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n"/>
@@ -1786,17 +1824,29 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>1.00286</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n"/>

--- a/test/4.10/净值.xlsx
+++ b/test/4.10/净值.xlsx
@@ -1038,7 +1038,7 @@
       <c r="B2" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1051,7 +1051,7 @@
       <c r="B3" s="0" t="n">
         <v>0.55</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>-26.6667%</t>
         </is>
@@ -1064,7 +1064,7 @@
       <c r="B4" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>-22.6667%</t>
         </is>
@@ -1077,7 +1077,7 @@
       <c r="B5" s="0" t="n">
         <v>0.62</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-17.3333%</t>
         </is>
@@ -1090,7 +1090,7 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>-10.6667%</t>
         </is>
@@ -1103,7 +1103,7 @@
       <c r="B7" s="0" t="n">
         <v>0.7111499999999999</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>-5.18%</t>
         </is>
@@ -1116,7 +1116,7 @@
       <c r="B8" s="0" t="n">
         <v>0.73668</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>-1.776%</t>
         </is>
@@ -1129,7 +1129,7 @@
       <c r="B9" s="0" t="n">
         <v>0.71105</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>-5.1933%</t>
         </is>
@@ -1142,7 +1142,7 @@
       <c r="B10" s="0" t="n">
         <v>0.8003</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1154,20 +1154,44 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>1.13204</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.13204</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n"/>
@@ -1193,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1215,7 +1239,7 @@
       <c r="B2" s="0" t="n">
         <v>0.63002</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1228,7 +1252,7 @@
       <c r="B3" s="0" t="n">
         <v>0.4115</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>-34.6846%</t>
         </is>
@@ -1241,7 +1265,7 @@
       <c r="B4" s="0" t="n">
         <v>0.4333</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>-31.2244%</t>
         </is>
@@ -1254,7 +1278,7 @@
       <c r="B5" s="0" t="n">
         <v>0.45555</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-27.6928%</t>
         </is>
@@ -1267,7 +1291,7 @@
       <c r="B6" s="0" t="n">
         <v>0.67</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1280,7 +1304,7 @@
       <c r="B7" s="0" t="n">
         <v>0.60005</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>-10.4403%</t>
         </is>
@@ -1293,7 +1317,7 @@
       <c r="B8" s="0" t="n">
         <v>0.73115</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1306,7 +1330,7 @@
       <c r="B9" s="0" t="n">
         <v>0.9115</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1319,7 +1343,7 @@
       <c r="B10" s="0" t="n">
         <v>0.8006</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>-12.1668%</t>
         </is>
@@ -1331,10 +1355,40 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1378,7 +1432,7 @@
       <c r="B2" s="0" t="n">
         <v>0.51555</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1391,7 +1445,7 @@
       <c r="B3" s="0" t="n">
         <v>0.23331</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>-54.7454%</t>
         </is>
@@ -1404,7 +1458,7 @@
       <c r="B4" s="0" t="n">
         <v>0.3815</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>-26.0014%</t>
         </is>
@@ -1417,7 +1471,7 @@
       <c r="B5" s="0" t="n">
         <v>0.45555</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-11.6381%</t>
         </is>
@@ -1430,7 +1484,7 @@
       <c r="B6" s="0" t="n">
         <v>0.5023</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>-2.5701%</t>
         </is>
@@ -1443,7 +1497,7 @@
       <c r="B7" s="0" t="n">
         <v>0.6112</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1456,7 +1510,7 @@
       <c r="B8" s="0" t="n">
         <v>0.7211</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1469,7 +1523,7 @@
       <c r="B9" s="0" t="n">
         <v>0.9883</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1482,7 +1536,7 @@
       <c r="B10" s="0" t="n">
         <v>0.8445</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>-14.5502%</t>
         </is>
@@ -1497,19 +1551,41 @@
       <c r="B11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n"/>
-      <c r="B12" s="0" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n"/>
-      <c r="B13" s="0" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n"/>
@@ -1564,7 +1640,7 @@
       <c r="B2" s="0" t="n">
         <v>0.4855</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1577,7 +1653,7 @@
       <c r="B3" s="0" t="n">
         <v>0.2112</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>-56.4985%</t>
         </is>
@@ -1590,7 +1666,7 @@
       <c r="B4" s="0" t="n">
         <v>0.3222</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>-33.6354%</t>
         </is>
@@ -1603,7 +1679,7 @@
       <c r="B5" s="0" t="n">
         <v>0.4112</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>-15.3038%</t>
         </is>
@@ -1616,7 +1692,7 @@
       <c r="B6" s="0" t="n">
         <v>0.5538</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1629,7 +1705,7 @@
       <c r="B7" s="0" t="n">
         <v>0.6223</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1642,7 +1718,7 @@
       <c r="B8" s="0" t="n">
         <v>0.7488</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1655,7 +1731,7 @@
       <c r="B9" s="0" t="n">
         <v>0.9211</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1668,7 +1744,7 @@
       <c r="B10" s="0" t="n">
         <v>0.8245</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>-10.4875%</t>
         </is>
@@ -1680,20 +1756,44 @@
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>1.00286</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025/04/10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n"/>
